--- a/examples/nemune-list-150-tajrobi-1404.xlsx
+++ b/examples/nemune-list-150-tajrobi-1404.xlsx
@@ -697,7 +697,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>36965</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -731,29 +731,41 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>فاقد خوابگاه</t>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>مخصوص داوطلبان بومی استان فارس</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>دارای تعهد خدمت یک و نیم برابر طول دوره تحصیل در پزشک قانونی شهرستان های استان فارس - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>159</t>
         </is>
       </c>
     </row>
@@ -763,7 +775,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>33227</t>
+          <t>37082</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -783,7 +795,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -793,16 +805,20 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
@@ -811,15 +827,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>فاقد خوابگاه</t>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان بومی استان بوشهر</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی بوشهر - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>127</t>
         </is>
       </c>
     </row>
@@ -829,7 +849,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>36965</t>
+          <t>37224</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -863,7 +883,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1</v>
@@ -874,30 +894,26 @@
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>مخصوص داوطلبان بومی استان فارس</t>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با ترتیب اولویت متقاضیان «بومی مناطق تحت پوشش دانشگاه علوم پزشکی زابل (شهرستانهای زابل، زهک، نیمروز، هامون، هیرمند)» و بعد «استان سیستانوبلوچستان» و در آخر «سایر استانها»</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>دارای تعهد خدمت یک و نیم برابر طول دوره تحصیل در پزشک قانونی شهرستان های استان فارس - محدودیت در ارائه خوابگاه</t>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی زابل - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>134</t>
         </is>
       </c>
     </row>
@@ -907,7 +923,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>37082</t>
+          <t>37316</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -941,7 +957,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1</v>
@@ -961,17 +977,17 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان بومی استان بوشهر</t>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان بومی استان فارس</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی بوشهر - محدودیت در ارائه خوابگاه</t>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی شیراز - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -981,7 +997,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>37224</t>
+          <t>37455</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1015,7 +1031,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>1</v>
@@ -1035,17 +1051,17 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>پذیرش از تمام متقاضیان سراسر کشور، با ترتیب اولویت متقاضیان «بومی مناطق تحت پوشش دانشگاه علوم پزشکی زابل (شهرستانهای زابل، زهک، نیمروز، هامون، هیرمند)» و بعد «استان سیستانوبلوچستان» و در آخر «سایر استانها»</t>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان بومی استان هرمزگان</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی زابل - محدودیت در ارائه خوابگاه</t>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی بندرعباس - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1071,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>37316</t>
+          <t>37456</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1089,7 +1105,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1</v>
@@ -1109,17 +1125,17 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان بومی استان فارس</t>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان بومی استان هرمزگان</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی شیراز - محدودیت در ارائه خوابگاه</t>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشکده علوم پزشکی و خدمات بهداشتی در مانی شرق استان هرمزگان (میناب) - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1145,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>37455</t>
+          <t>37223</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1159,11 +1175,11 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1</v>
@@ -1183,17 +1199,17 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان بومی استان هرمزگان</t>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با ترتیب اولویت متقاضیان «بومی مناطق تحت پوشش دانشگاه علوم پزشکی زاهدان (شهرستانهای تفتان، خاش، زاهدان، سراوان، سیب سوران، گلشن، میرجاوه)» و بعد «استان سیستانوبلوچستان» و در آخر «سایر استانها»</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی بندرعباس - محدودیت در ارائه خوابگاه</t>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی زاهدان - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>131</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1219,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>37456</t>
+          <t>37225</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1233,11 +1249,11 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1</v>
@@ -1257,17 +1273,17 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان بومی استان هرمزگان</t>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با ترتیب اولویت متقاضیان «بومی مناطق تحت پوشش دانشگاه علوم پزشکی ایرانشهر (شهرستانهای ایرانشهر، بمپور، دلگان، راسک، سرباز، فنوج، لاشار، مهرستان)» و بعد «استان سیستانوبلوچستان» و در آخر «سایر استانها»</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشکده علوم پزشکی و خدمات بهداشتی در مانی شرق استان هرمزگان (میناب) - محدودیت در ارائه خوابگاه</t>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی ایرانشهر - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>137</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1293,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>37223</t>
+          <t>37226</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1311,7 +1327,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1</v>
@@ -1331,17 +1347,17 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>پذیرش از تمام متقاضیان سراسر کشور، با ترتیب اولویت متقاضیان «بومی مناطق تحت پوشش دانشگاه علوم پزشکی زاهدان (شهرستانهای تفتان، خاش، زاهدان، سراوان، سیب سوران، گلشن، میرجاوه)» و بعد «استان سیستانوبلوچستان» و در آخر «سایر استانها»</t>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان «بومی مناطق تحت پوشش دانشکده علوم پزشکی و خدمات بهداشتی درمانی چابهار (شهرستانهای چابهار، دشتیاری، زرآباد، قصرقند، کنارک، نیکشهر)» و بعد «استان سیستانوبلوچستان» و در آخر «سایر استانها»</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی زاهدان - محدودیت در ارائه خوابگاه</t>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشکده علوم پزشکی و خدمات بهداشتی درمانی چابهار - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>140</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1367,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>37225</t>
+          <t>37454</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1385,7 +1401,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1</v>
@@ -1405,17 +1421,17 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>پذیرش از تمام متقاضیان سراسر کشور، با ترتیب اولویت متقاضیان «بومی مناطق تحت پوشش دانشگاه علوم پزشکی ایرانشهر (شهرستانهای ایرانشهر، بمپور، دلگان، راسک، سرباز، فنوج، لاشار، مهرستان)» و بعد «استان سیستانوبلوچستان» و در آخر «سایر استانها»</t>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان بومی استان هرمزگان</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی ایرانشهر - محدودیت در ارائه خوابگاه</t>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشکده علوم پزشکی و خدمات بهداشتی در مانی غرب استان هرمزگان (بندرلنگه) - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1441,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>37226</t>
+          <t>32178</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1435,12 +1451,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شیراز</t>
+          <t>دانشگاه علوم پزشکی بوشهر</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>بوشهر</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1455,20 +1471,16 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
@@ -1477,19 +1489,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان «بومی مناطق تحت پوشش دانشکده علوم پزشکی و خدمات بهداشتی درمانی چابهار (شهرستانهای چابهار، دشتیاری، زرآباد، قصرقند، کنارک، نیکشهر)» و بعد «استان سیستانوبلوچستان» و در آخر «سایر استانها»</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشکده علوم پزشکی و خدمات بهداشتی درمانی چابهار - محدودیت در ارائه خوابگاه</t>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1507,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>37454</t>
+          <t>32011</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1509,12 +1517,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شیراز</t>
+          <t>دانشگاه علوم پزشکی اصفهان</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>اصفهان</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1529,20 +1537,16 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
@@ -1551,19 +1555,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان بومی استان هرمزگان</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشکده علوم پزشکی و خدمات بهداشتی در مانی غرب استان هرمزگان (بندرلنگه) - محدودیت در ارائه خوابگاه</t>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>32178</t>
+          <t>33179</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی بوشهر</t>
+          <t>دانشگاه علوم پزشکی جهرم</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>بوشهر</t>
+          <t>فارس</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1</v>
@@ -1624,12 +1624,12 @@
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+          <t>محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>89</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>33330</t>
+          <t>33287</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه آزاد اسلامی استان فارس - واحد کازرون</t>
+          <t>دانشگاه علوم پزشکی فسا</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>آزاد تمام وقت</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1</v>
@@ -1688,10 +1688,14 @@
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>سال اول معرفی به خوابگاه خودگردان</t>
+        </is>
+      </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>93</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1705,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>32014</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1711,17 +1715,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه آزاد اسلامی استان فارس - واحد کازرون</t>
+          <t>دانشگاه علوم پزشکی اصفهان</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>اصفهان</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>خودگردان آزاد</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1731,11 +1735,11 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>1</v>
@@ -1750,10 +1754,14 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>محدودیت در ارائه خوابگاه</t>
+        </is>
+      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1771,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>32011</t>
+          <t>33943</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1773,12 +1781,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی اصفهان</t>
+          <t>دانشگاه علوم پزشکی بندرعباس</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>هرمزگان</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1797,7 +1805,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>1</v>
@@ -1814,12 +1822,12 @@
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>محدودیت در ارائه خوابگاه</t>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>117</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1837,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>32203</t>
+          <t>33181</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1839,17 +1847,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی بوشهر</t>
+          <t>دانشگاه علوم پزشکی جهرم</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>بوشهر</t>
+          <t>فارس</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1859,11 +1867,11 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1</v>
@@ -1880,12 +1888,12 @@
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+          <t>محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>89</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1903,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>33179</t>
+          <t>33278</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1903,9 +1911,9 @@
           <t>دکتری عمومی پزشکی</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>دانشگاه علوم پزشکی جهرم</t>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>دانشگاه علوم پزشکی شیراز (محل تحصیل دانشکده علوم پزشکی لارستان)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1925,11 +1933,11 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>1</v>
@@ -1944,14 +1952,14 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>محدودیت در ارائه خوابگاه</t>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>ممنوعیت نقل و انتقال به دانشگاه علوم پزشکی شیراز</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>93</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1969,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>33287</t>
+          <t>33279</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1969,9 +1977,9 @@
           <t>دکتری عمومی پزشکی</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>دانشگاه علوم پزشکی فسا</t>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>دانشگاه علوم پزشکی شیراز (محل تحصیل دانشکده علوم پزشکی گراش)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1991,11 +1999,11 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1</v>
@@ -2010,9 +2018,9 @@
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>سال اول معرفی به خوابگاه خودگردان</t>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>ممنوعیت نقل و انتقال به دانشگاه علوم پزشکی شیراز</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -2027,7 +2035,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>33288</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2037,12 +2045,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی اصفهان</t>
+          <t>دانشگاه علوم پزشکی فسا</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>فارس</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2061,7 +2069,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1</v>
@@ -2078,12 +2086,12 @@
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>محدودیت در ارائه خوابگاه</t>
+          <t>سال اول معرفی به خوابگاه خودگردان</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>93</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2101,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>33943</t>
+          <t>32273</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2103,12 +2111,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی بندرعباس</t>
+          <t>دانشگاه علوم پزشکی ایران</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>هرمزگان</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2127,7 +2135,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>20</v>
+        <v>128</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>1</v>
@@ -2144,12 +2152,12 @@
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>فاقد خوابگاه</t>
+          <t>دارای خوابگاه ملکی</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2167,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>33181</t>
+          <t>32326</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2169,12 +2177,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی جهرم</t>
+          <t>دانشگاه علوم پزشکی تهران</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2189,11 +2197,11 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>1</v>
@@ -2208,14 +2216,10 @@
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr"/>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>محدودیت در ارائه خوابگاه</t>
-        </is>
-      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>61</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2229,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>33278</t>
+          <t>32364</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2233,14 +2237,14 @@
           <t>دکتری عمومی پزشکی</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>دانشگاه علوم پزشکی شیراز (محل تحصیل دانشکده علوم پزشکی لارستان)</t>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2255,11 +2259,11 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1</v>
@@ -2274,14 +2278,10 @@
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr"/>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t>ممنوعیت نقل و انتقال به دانشگاه علوم پزشکی شیراز</t>
-        </is>
-      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>33279</t>
+          <t>33946</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2299,14 +2299,14 @@
           <t>دکتری عمومی پزشکی</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>دانشگاه علوم پزشکی شیراز (محل تحصیل دانشکده علوم پزشکی گراش)</t>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>دانشگاه علوم پزشکی بندرعباس</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>هرمزگان</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1</v>
@@ -2340,14 +2340,14 @@
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr"/>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t>ممنوعیت نقل و انتقال به دانشگاه علوم پزشکی شیراز</t>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>117</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>33288</t>
+          <t>32071</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی فسا</t>
+          <t>دانشگاه علوم پزشکی کاشان</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>اصفهان</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2387,11 +2387,11 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>1</v>
@@ -2408,12 +2408,12 @@
       <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>سال اول معرفی به خوابگاه خودگردان</t>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>33192</t>
+          <t>33598</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2433,17 +2433,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی جهرم</t>
+          <t>دانشگاه علوم پزشکی یاسوج</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>کهگیلویه و بویراحمد</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>1</v>
@@ -2474,12 +2474,12 @@
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>105</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>33299</t>
+          <t>32274</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی فسا</t>
+          <t>دانشگاه علوم پزشکی ایران</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>1</v>
@@ -2531,11 +2531,7 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -2544,12 +2540,12 @@
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>سال اول معرفی به خوابگاه خودگردان</t>
+          <t>دارای خوابگاه ملکی</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2555,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>32046</t>
+          <t>32328</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2569,17 +2565,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی اصفهان</t>
+          <t>دانشگاه علوم پزشکی تهران</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2593,7 +2589,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>1</v>
@@ -2608,14 +2604,10 @@
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr"/>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>معرفی به خوابگاههای خودگردان</t>
-        </is>
-      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>61</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2617,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>32273</t>
+          <t>32366</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2635,7 +2627,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی ایران</t>
+          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2655,11 +2647,11 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1</v>
@@ -2674,14 +2666,10 @@
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr"/>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>دارای خوابگاه ملکی</t>
-        </is>
-      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2679,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>32326</t>
+          <t>31801</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2701,12 +2689,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تهران</t>
+          <t>دانشگاه علوم پزشکی تبریز</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>آذربایجان شرقی</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2725,7 +2713,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>1</v>
@@ -2743,7 +2731,7 @@
       <c r="Q33" s="2" t="inlineStr"/>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2741,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>32364</t>
+          <t>32634</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2763,12 +2751,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
+          <t>دانشگاه علوم پزشکی مشهد</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>خراسان رضوی</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2787,7 +2775,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1</v>
@@ -2802,10 +2790,14 @@
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
+        </is>
+      </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2807,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>33946</t>
+          <t>37072</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2825,12 +2817,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی بندرعباس</t>
+          <t>دانشگاه علوم پزشکی جهرم</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>هرمزگان</t>
+          <t>فارس</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2845,16 +2837,20 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
@@ -2863,15 +2859,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr"/>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>فاقد خوابگاه</t>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان بومی استان بوشهر</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی بوشهر - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>127</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>32071</t>
+          <t>37317</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی کاشان</t>
+          <t>دانشگاه علوم پزشکی فسا</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>فارس</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2915,12 +2915,16 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
@@ -2929,15 +2933,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr"/>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان بومی استان فارس</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>دارای تعهد خدمت یک و نیم برابر طول دوره تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی فسا - سال اول معرفی به خوابگاه خودگردان</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2955,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>33974</t>
+          <t>37330</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2957,17 +2965,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی بندرعباس</t>
+          <t>دانشگاه علوم پزشکی جهرم</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>هرمزگان</t>
+          <t>فارس</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2981,12 +2989,16 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
@@ -2995,15 +3007,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr"/>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>فاقد خوابگاه</t>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان بومی استان کردستان</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>دارای تعهد خدمت یک و نیم برابر طول دوره تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی کردستان - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>142</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3029,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>34003</t>
+          <t>37357</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3023,17 +3039,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه آزاد اسلامی واحد خودگردان قشم</t>
+          <t>دانشگاه علوم پزشکی جهرم</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>هرمزگان</t>
+          <t>فارس</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>خودگردان آزاد</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -3047,12 +3063,16 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
@@ -3061,15 +3081,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان بومی استان گلستان</t>
+        </is>
+      </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>دوره علوم پایه و مقدمات بالینی در جزیره قشم و دوره بالینی در بندرعباس برگزار می گردد. ضمنا شهریه پذیرفته شدگان مرکز فوق براساس شهریه واحدهای بین المللی دانشگاه آزاد اسلامی می باشد.</t>
+          <t>دارای تعهد خدمت یک و نیم برابر طول دوره تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی گلستان - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>143</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3103,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>33193</t>
+          <t>37421</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3099,7 +3123,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3109,7 +3133,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
@@ -3118,7 +3142,11 @@
       <c r="J39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
@@ -3127,15 +3155,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان بومی استان هرمزگان</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی بندرعباس - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>147</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3243,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>33229</t>
+          <t>36969</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3231,7 +3263,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3250,24 +3282,36 @@
       <c r="J41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr"/>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>فاقد خوابگاه</t>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>مخصوص داوطلبان بومی استان فارس</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشکده علوم پزشکی لارستان - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>159</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3321,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>36969</t>
+          <t>37305</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3311,7 +3355,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>2</v>
@@ -3322,30 +3366,26 @@
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>مخصوص داوطلبان بومی استان فارس</t>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با ترتیب اولویت متقاضیان «بومی مناطق تحت پوشش دانشگاه علوم پزشکی ایرانشهر (شهرستانهای ایرانشهر، بمپور، دلگان، راسک، سرباز، فنوج، لاشار، مهرستان)» و بعد «استان سیستانوبلوچستان» و در آخر «سایر استانها»</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشکده علوم پزشکی لارستان - محدودیت در ارائه خوابگاه</t>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی ایرانشهر - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>138</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3395,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>37305</t>
+          <t>37306</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3409,17 +3449,17 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>پذیرش از تمام متقاضیان سراسر کشور، با ترتیب اولویت متقاضیان «بومی مناطق تحت پوشش دانشگاه علوم پزشکی ایرانشهر (شهرستانهای ایرانشهر، بمپور، دلگان، راسک، سرباز، فنوج، لاشار، مهرستان)» و بعد «استان سیستانوبلوچستان» و در آخر «سایر استانها»</t>
+          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان «بومی مناطق تحت پوشش دانشکده علوم پزشکی و خدمات بهداشتی درمانی چابهار (شهرستانهای چابهار، دشتیاری، زرآباد، قصرقند، کنارک، نیکشهر)» و بعد «استان سیستانوبلوچستان» و در آخر «سایر استانها»</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشگاه علوم پزشکی ایرانشهر - محدودیت در ارائه خوابگاه</t>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشکده علوم پزشکی و خدمات بهداشتی درمانی چابهار - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3469,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>37306</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3439,12 +3479,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شیراز</t>
+          <t>دانشگاه علوم پزشکی بوشهر</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>بوشهر</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3463,16 +3503,12 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
@@ -3481,19 +3517,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t>پذیرش از تمام متقاضیان سراسر کشور، با اولویت متقاضیان «بومی مناطق تحت پوشش دانشکده علوم پزشکی و خدمات بهداشتی درمانی چابهار (شهرستانهای چابهار، دشتیاری، زرآباد، قصرقند، کنارک، نیکشهر)» و بعد «استان سیستانوبلوچستان» و در آخر «سایر استانها»</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشکده علوم پزشکی و خدمات بهداشتی درمانی چابهار - محدودیت در ارائه خوابگاه</t>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3535,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>33328</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3513,17 +3545,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه آزاد اسلامی استان فارس - واحد شیراز</t>
+          <t>دانشگاه علوم پزشکی اصفهان</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>اصفهان</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>آزاد تمام وقت</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3537,7 +3569,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>2</v>
@@ -3552,10 +3584,14 @@
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr"/>
-      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>محدودیت در ارائه خوابگاه</t>
+        </is>
+      </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3601,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>33329</t>
+          <t>33948</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3575,17 +3611,17 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه آزاد اسلامی استان فارس - واحد شیراز</t>
+          <t>دانشگاه علوم پزشکی بندرعباس</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>هرمزگان</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>خودگردان آزاد</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -3599,7 +3635,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>2</v>
@@ -3607,21 +3643,21 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr"/>
-      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>فاقد خوابگاه</t>
+        </is>
+      </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>117</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3667,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>32181</t>
+          <t>32330</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3641,12 +3677,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی بوشهر</t>
+          <t>دانشگاه علوم پزشکی تهران</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>بوشهر</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -3665,7 +3701,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>2</v>
@@ -3680,14 +3716,10 @@
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr"/>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
-        </is>
-      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>61</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3729,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>32016</t>
+          <t>32369</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3707,12 +3739,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی اصفهان</t>
+          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3731,7 +3763,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>2</v>
@@ -3746,14 +3778,10 @@
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr"/>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>محدودیت در ارائه خوابگاه</t>
-        </is>
-      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3791,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>32068</t>
+          <t>32074</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3773,7 +3801,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی اصفهان</t>
+          <t>دانشگاه علوم پزشکی کاشان</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3783,7 +3811,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -3797,7 +3825,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>2</v>
@@ -3812,9 +3840,9 @@
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr"/>
-      <c r="Q49" s="3" t="inlineStr">
-        <is>
-          <t>محل تحصیل پردیس خودگردان دانشگاه - معرفی به خوابگاههای خودگردان</t>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
@@ -3829,7 +3857,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3839,12 +3867,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی بندرعباس</t>
+          <t>دانشگاه علوم پزشکی یاسوج</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>هرمزگان</t>
+          <t>کهگیلویه و بویراحمد</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3863,7 +3891,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>2</v>
@@ -3885,7 +3913,7 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>105</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3923,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>32330</t>
+          <t>32370</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3905,7 +3933,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تهران</t>
+          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3925,11 +3953,11 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>2</v>
@@ -3947,7 +3975,7 @@
       <c r="Q51" s="2" t="inlineStr"/>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3985,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>32369</t>
+          <t>31806</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3967,12 +3995,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
+          <t>دانشگاه علوم پزشکی تبریز</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>آذربایجان شرقی</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3991,7 +4019,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>2</v>
@@ -4009,7 +4037,7 @@
       <c r="Q52" s="2" t="inlineStr"/>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4047,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>32074</t>
+          <t>32639</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4029,12 +4057,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی کاشان</t>
+          <t>دانشگاه علوم پزشکی مشهد</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>خراسان رضوی</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -4053,7 +4081,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>2</v>
@@ -4075,7 +4103,7 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4113,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>34090</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4095,12 +4123,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی یاسوج</t>
+          <t>دانشگاه علوم پزشکی یزد</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>کهگیلویه و بویراحمد</t>
+          <t>یزد</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -4119,7 +4147,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>2</v>
@@ -4136,12 +4164,12 @@
       <c r="P54" s="2" t="inlineStr"/>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>فاقد خوابگاه</t>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>122</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4179,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>32370</t>
+          <t>31808</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4161,12 +4189,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
+          <t>دانشگاه علوم پزشکی تبریز</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>آذربایجان شرقی</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -4185,7 +4213,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>2</v>
@@ -4203,7 +4231,7 @@
       <c r="Q55" s="2" t="inlineStr"/>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4241,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>31806</t>
+          <t>32640</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4223,12 +4251,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تبریز</t>
+          <t>دانشگاه علوم پزشکی مشهد</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>آذربایجان شرقی</t>
+          <t>خراسان رضوی</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -4243,11 +4271,11 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>2</v>
@@ -4262,10 +4290,14 @@
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr"/>
-      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
+        </is>
+      </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4307,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>32639</t>
+          <t>31907</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4285,12 +4317,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی مشهد</t>
+          <t>دانشگاه علوم پزشکی ارومیه</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>خراسان رضوی</t>
+          <t>آذربایجان غربی</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -4309,7 +4341,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>2</v>
@@ -4331,7 +4363,7 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4373,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>32363</t>
+          <t>31971</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4351,17 +4383,17 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تهران</t>
+          <t>دانشگاه علوم پزشکی اردبیل</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>اردبیل</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -4375,7 +4407,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>2</v>
@@ -4390,14 +4422,14 @@
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr"/>
-      <c r="Q58" s="3" t="inlineStr">
-        <is>
-          <t>محل تحصیل پردیس خودگردان دانشگاه واقع در تهران - فاقد خوابگاه</t>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4439,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>32401</t>
+          <t>32118</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4417,17 +4449,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
+          <t>دانشگاه علوم پزشکی البرز - کرج</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>البرز</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -4441,7 +4473,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>2</v>
@@ -4463,7 +4495,7 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4505,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>34090</t>
+          <t>32148</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4483,12 +4515,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی یزد</t>
+          <t>دانشگاه علوم پزشکی ایلام</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>یزد</t>
+          <t>ایلام</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -4507,7 +4539,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>2</v>
@@ -4529,7 +4561,7 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4571,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>32106</t>
+          <t>32452</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4547,19 +4579,19 @@
           <t>دکتری عمومی دندانپزشکی</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>دانشگاه آزاد اسلامی استان اصفهان - واحد خوراسگان</t>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>دانشگاه علوم پزشکی شهرکرد</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>چهارمحال و بختیاری</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>آزاد تمام وقت</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -4573,7 +4605,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>2</v>
@@ -4588,10 +4620,14 @@
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr"/>
-      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
+        </is>
+      </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>65</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4637,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>32108</t>
+          <t>32486</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4609,19 +4645,19 @@
           <t>دکتری عمومی دندانپزشکی</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>دانشگاه آزاد اسلامی استان اصفهان - واحد خوراسگان</t>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>دانشگاه علوم پزشکی بیرجند</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>خراسان جنوبی</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>خودگردان آزاد</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -4635,7 +4671,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>2</v>
@@ -4650,10 +4686,14 @@
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr"/>
-      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
+        </is>
+      </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4703,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>31808</t>
+          <t>32796</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4673,12 +4713,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تبریز</t>
+          <t>دانشگاه علوم پزشکی جندیشاپور - اهواز</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>آذربایجان شرقی</t>
+          <t>خوزستان</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -4693,11 +4733,11 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>2</v>
@@ -4715,7 +4755,7 @@
       <c r="Q63" s="2" t="inlineStr"/>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>76</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4765,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>32640</t>
+          <t>32958</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4735,12 +4775,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی مشهد</t>
+          <t>دانشگاه علوم پزشکی زنجان</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>خراسان رضوی</t>
+          <t>زنجان</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -4755,11 +4795,11 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>2</v>
@@ -4776,12 +4816,12 @@
       <c r="P64" s="2" t="inlineStr"/>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>82</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4831,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>32402</t>
+          <t>33002</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4801,17 +4841,17 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
+          <t>دانشگاه علوم پزشکی سمنان</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>سمنان</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -4821,11 +4861,11 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>2</v>
@@ -4842,12 +4882,12 @@
       <c r="P65" s="2" t="inlineStr"/>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>فاقد خوابگاه</t>
+          <t>محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>83</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4897,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>31843</t>
+          <t>33107</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4867,17 +4907,17 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تبریز</t>
+          <t>دانشگاه علوم پزشکی زاهدان</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>آذربایجان شرقی</t>
+          <t>سیستان و بلوچستان</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -4891,7 +4931,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>2</v>
@@ -4899,11 +4939,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -4912,12 +4948,12 @@
       <c r="P66" s="2" t="inlineStr"/>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>فاقد خوابگاه</t>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>87</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4963,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>31900</t>
+          <t>33334</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4937,17 +4973,17 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه آزاد اسلامی واحد علوم پزشکی تبریز</t>
+          <t>دانشگاه علوم پزشکی قزوین</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>آذربایجان شرقی</t>
+          <t>قزوین</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>آزاد تمام وقت</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -4961,7 +4997,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>2</v>
@@ -4976,10 +5012,14 @@
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr"/>
-      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>فاقد خوابگاه</t>
+        </is>
+      </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>95</t>
         </is>
       </c>
     </row>
@@ -4989,7 +5029,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>33397</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4999,17 +5039,17 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه آزاد اسلامی واحد علوم پزشکی تبریز</t>
+          <t>دانشگاه علوم پزشکی کردستان - سنندج</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>آذربایجان شرقی</t>
+          <t>کردستان</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>خودگردان آزاد</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -5023,7 +5063,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>2</v>
@@ -5031,21 +5071,21 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr"/>
-      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>فاقد خوابگاه</t>
+        </is>
+      </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>98</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5095,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>32668</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5065,17 +5105,17 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی مشهد</t>
+          <t>دانشگاه علوم پزشکی رفسنجان</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>خراسان رضوی</t>
+          <t>کرمان</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -5089,7 +5129,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>2</v>
@@ -5097,11 +5137,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr"/>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5110,12 +5146,12 @@
       <c r="P69" s="2" t="inlineStr"/>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+          <t>معرفی به خوابگاههای خودگردان</t>
         </is>
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5161,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>32107</t>
+          <t>33490</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5133,19 +5169,19 @@
           <t>دکتری عمومی دندانپزشکی</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>دانشگاه آزاد اسلامی استان اصفهان - واحد خوراسگان</t>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>دانشگاه علوم پزشکی کرمان</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>کرمان</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>آزاد تمام وقت</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -5155,11 +5191,11 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>2</v>
@@ -5174,10 +5210,14 @@
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr"/>
-      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>فاقد خوابگاه</t>
+        </is>
+      </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5227,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>32109</t>
+          <t>33547</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5195,19 +5235,19 @@
           <t>دکتری عمومی دندانپزشکی</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>دانشگاه آزاد اسلامی استان اصفهان - واحد خوراسگان</t>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>دانشگاه علوم پزشکی کرمانشاه</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>کرمانشاه</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>خودگردان آزاد</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -5217,11 +5257,11 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>2</v>
@@ -5236,10 +5276,14 @@
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr"/>
-      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
+        </is>
+      </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>103</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5293,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>31844</t>
+          <t>33658</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5259,17 +5303,17 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تبریز</t>
+          <t>دانشگاه علوم پزشکی گیلان - رشت</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>آذربایجان شرقی</t>
+          <t>گیلان</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -5279,11 +5323,11 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>2</v>
@@ -5291,11 +5335,7 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5304,12 +5344,12 @@
       <c r="P72" s="2" t="inlineStr"/>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>فاقد خوابگاه</t>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>107</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5425,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>33228</t>
+          <t>36967</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5405,7 +5445,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -5419,29 +5459,45 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P74" s="2" t="inlineStr"/>
-      <c r="Q74" s="2" t="inlineStr">
-        <is>
-          <t>فاقد خوابگاه</t>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>مخصوص داوطلبان بومی استان فارس</t>
+        </is>
+      </c>
+      <c r="Q74" s="3" t="inlineStr">
+        <is>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشکده علوم پزشکی و خدمات بهداشتی درمانی گراش - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>159</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5507,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>36967</t>
+          <t>36968</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5518,7 +5574,7 @@
       </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
-          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشکده علوم پزشکی و خدمات بهداشتی درمانی گراش - محدودیت در ارائه خوابگاه</t>
+          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشکده علوم پزشکی و خدمات بهداشتی درمانی لارستان - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R75" s="2" t="inlineStr">
@@ -5533,7 +5589,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>36968</t>
+          <t>32015</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5543,12 +5599,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شیراز</t>
+          <t>دانشگاه علوم پزشکی اصفهان</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>اصفهان</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -5567,45 +5623,29 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>مخصوص داوطلبان بومی استان فارس</t>
-        </is>
-      </c>
-      <c r="Q76" s="3" t="inlineStr">
-        <is>
-          <t>دارای تعهد خدمت یک و نیم برابر طول مدت تحصیل در مناطق مورد نیاز دانشکده علوم پزشکی و خدمات بهداشتی درمانی لارستان - محدودیت در ارائه خوابگاه</t>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5655,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>32015</t>
+          <t>33947</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5625,12 +5665,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی اصفهان</t>
+          <t>دانشگاه علوم پزشکی بندرعباس</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>هرمزگان</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -5649,7 +5689,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>3</v>
@@ -5666,12 +5706,12 @@
       <c r="P77" s="2" t="inlineStr"/>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>محدودیت در ارائه خوابگاه</t>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>117</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5721,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>32047</t>
+          <t>32275</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5691,17 +5731,17 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی اصفهان</t>
+          <t>دانشگاه علوم پزشکی ایران</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -5715,7 +5755,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>3</v>
@@ -5732,12 +5772,12 @@
       <c r="P78" s="2" t="inlineStr"/>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>معرفی به خوابگاههای خودگردان</t>
+          <t>دارای خوابگاه ملکی</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5787,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>33947</t>
+          <t>32329</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5757,12 +5797,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی بندرعباس</t>
+          <t>دانشگاه علوم پزشکی تهران</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>هرمزگان</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -5781,7 +5821,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>3</v>
@@ -5796,14 +5836,10 @@
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr"/>
-      <c r="Q79" s="2" t="inlineStr">
-        <is>
-          <t>فاقد خوابگاه</t>
-        </is>
-      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>61</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5849,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>32275</t>
+          <t>32367</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5823,7 +5859,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی ایران</t>
+          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -5847,7 +5883,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>3</v>
@@ -5862,14 +5898,10 @@
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr"/>
-      <c r="Q80" s="2" t="inlineStr">
-        <is>
-          <t>دارای خوابگاه ملکی</t>
-        </is>
-      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5911,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>32329</t>
+          <t>31804</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5889,12 +5921,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تهران</t>
+          <t>دانشگاه علوم پزشکی تبریز</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>آذربایجان شرقی</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -5913,7 +5945,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>3</v>
@@ -5931,7 +5963,7 @@
       <c r="Q81" s="2" t="inlineStr"/>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5973,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>32367</t>
+          <t>32637</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5951,12 +5983,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
+          <t>دانشگاه علوم پزشکی مشهد</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>خراسان رضوی</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -5975,7 +6007,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>3</v>
@@ -5990,10 +6022,14 @@
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr"/>
-      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
+        </is>
+      </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6039,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>33976</t>
+          <t>34088</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6013,17 +6049,17 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی بندرعباس</t>
+          <t>دانشگاه علوم پزشکی یزد</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>هرمزگان</t>
+          <t>یزد</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -6037,7 +6073,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>3</v>
@@ -6054,12 +6090,12 @@
       <c r="P83" s="2" t="inlineStr"/>
       <c r="Q83" s="2" t="inlineStr">
         <is>
-          <t>فاقد خوابگاه</t>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>122</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6105,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31804</t>
+          <t>31805</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6099,7 +6135,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
@@ -6131,7 +6167,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>32637</t>
+          <t>32638</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6161,11 +6197,11 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>3</v>
@@ -6187,7 +6223,7 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6233,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>32300</t>
+          <t>31906</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6207,17 +6243,17 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی ایران</t>
+          <t>دانشگاه علوم پزشکی ارومیه</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>آذربایجان غربی</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -6231,7 +6267,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>3</v>
@@ -6248,12 +6284,12 @@
       <c r="P86" s="2" t="inlineStr"/>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>فاقد خوابگاه</t>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6299,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>32362</t>
+          <t>31969</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6273,17 +6309,17 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تهران</t>
+          <t>دانشگاه علوم پزشکی اردبیل</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>اردبیل</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -6297,7 +6333,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>3</v>
@@ -6312,14 +6348,14 @@
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr"/>
-      <c r="Q87" s="3" t="inlineStr">
-        <is>
-          <t>محل تحصیل پردیس خودگردان دانشگاه واقع در تهران - فاقد خوابگاه</t>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6365,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>32400</t>
+          <t>32117</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6339,17 +6375,17 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
+          <t>دانشگاه علوم پزشکی البرز - کرج</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>البرز</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -6363,7 +6399,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>3</v>
@@ -6385,7 +6421,7 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6431,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>34088</t>
+          <t>32485</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6405,12 +6441,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی یزد</t>
+          <t>دانشگاه علوم پزشکی بیرجند</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>یزد</t>
+          <t>خراسان جنوبی</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -6429,7 +6465,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>3</v>
@@ -6451,7 +6487,7 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6497,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31805</t>
+          <t>32794</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -6471,12 +6507,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تبریز</t>
+          <t>دانشگاه علوم پزشکی جندیشاپور - اهواز</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>آذربایجان شرقی</t>
+          <t>خوزستان</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -6491,11 +6527,11 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>3</v>
@@ -6513,7 +6549,7 @@
       <c r="Q90" s="2" t="inlineStr"/>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>76</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6559,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>32638</t>
+          <t>32956</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6533,12 +6569,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی مشهد</t>
+          <t>دانشگاه علوم پزشکی زنجان</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>خراسان رضوی</t>
+          <t>زنجان</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -6553,11 +6589,11 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>3</v>
@@ -6574,12 +6610,12 @@
       <c r="P91" s="2" t="inlineStr"/>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>82</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6625,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>33001</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6599,17 +6635,17 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تبریز</t>
+          <t>دانشگاه علوم پزشکی سمنان</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>آذربایجان شرقی</t>
+          <t>سمنان</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -6623,7 +6659,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>3</v>
@@ -6640,12 +6676,12 @@
       <c r="P92" s="2" t="inlineStr"/>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>فاقد خوابگاه</t>
+          <t>محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>83</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6691,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>32666</t>
+          <t>33489</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6665,17 +6701,17 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی مشهد</t>
+          <t>دانشگاه علوم پزشکی کرمان</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>خراسان رضوی</t>
+          <t>کرمان</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -6689,7 +6725,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>3</v>
@@ -6706,12 +6742,12 @@
       <c r="P93" s="2" t="inlineStr"/>
       <c r="Q93" s="2" t="inlineStr">
         <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6757,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>34126</t>
+          <t>33546</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6731,17 +6767,17 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی یزد</t>
+          <t>دانشگاه علوم پزشکی کرمانشاه</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>یزد</t>
+          <t>کرمانشاه</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -6755,7 +6791,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>3</v>
@@ -6770,14 +6806,14 @@
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr"/>
-      <c r="Q94" s="3" t="inlineStr">
-        <is>
-          <t>محل تحصیل دانشکده داروسازی یزد - عدم تعهد در واگذاری خوابگاه</t>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>103</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6823,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>31842</t>
+          <t>33693</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6797,17 +6833,17 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تبریز</t>
+          <t>دانشگاه علوم پزشکی گیلان - رشت</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>آذربایجان شرقی</t>
+          <t>گیلان</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -6817,11 +6853,11 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>3</v>
@@ -6836,14 +6872,14 @@
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr"/>
-      <c r="Q95" s="2" t="inlineStr">
-        <is>
-          <t>فاقد خوابگاه</t>
+      <c r="Q95" s="3" t="inlineStr">
+        <is>
+          <t>محل تحصیل دانشکده داروسازی - عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>107</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6889,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>32667</t>
+          <t>33737</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6863,17 +6899,17 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی مشهد</t>
+          <t>دانشگاه علوم پزشکی لرستان - خرم آباد</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>خراسان رضوی</t>
+          <t>لرستان</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -6883,11 +6919,11 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>3</v>
@@ -6902,14 +6938,14 @@
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr"/>
-      <c r="Q96" s="2" t="inlineStr">
-        <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+      <c r="Q96" s="3" t="inlineStr">
+        <is>
+          <t>محل تحصیل دانشکده داروسازی خرم آباد - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>110</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6955,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>31906</t>
+          <t>33765</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6929,12 +6965,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی ارومیه</t>
+          <t>دانشگاه علوم پزشکی بابل</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>آذربایجان غربی</t>
+          <t>مازندران</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -6953,7 +6989,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>3</v>
@@ -6970,12 +7006,12 @@
       <c r="P97" s="2" t="inlineStr"/>
       <c r="Q97" s="2" t="inlineStr">
         <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>111</t>
         </is>
       </c>
     </row>
@@ -6985,7 +7021,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31969</t>
+          <t>33798</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -6995,12 +7031,12 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی اردبیل</t>
+          <t>دانشگاه علوم پزشکی مازندران - ساری</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>اردبیل</t>
+          <t>مازندران</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -7019,7 +7055,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>3</v>
@@ -7034,14 +7070,10 @@
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr"/>
-      <c r="Q98" s="2" t="inlineStr">
-        <is>
-          <t>فاقد خوابگاه</t>
-        </is>
-      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>112</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7083,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>32117</t>
+          <t>34007</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7061,12 +7093,12 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی البرز - کرج</t>
+          <t>دانشگاه علوم پزشکی همدان</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>البرز</t>
+          <t>همدان</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -7102,12 +7134,12 @@
       <c r="P99" s="2" t="inlineStr"/>
       <c r="Q99" s="2" t="inlineStr">
         <is>
-          <t>فاقد خوابگاه</t>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7215,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>33238</t>
+          <t>32037</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7193,17 +7225,17 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شیراز</t>
+          <t>دانشگاه علوم پزشکی اصفهان</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>اصفهان</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -7217,7 +7249,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>4</v>
@@ -7226,16 +7258,20 @@
       <c r="L101" s="2" t="inlineStr"/>
       <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr"/>
-      <c r="O101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P101" s="2" t="inlineStr"/>
       <c r="Q101" s="2" t="inlineStr">
         <is>
-          <t>فاقد خوابگاه</t>
+          <t>محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -7245,7 +7281,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>32037</t>
+          <t>32291</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7255,12 +7291,12 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی اصفهان</t>
+          <t>دانشگاه علوم پزشکی ایران</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -7296,12 +7332,12 @@
       <c r="P102" s="2" t="inlineStr"/>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>محدودیت در ارائه خوابگاه</t>
+          <t>دارای خوابگاه ملکی</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -7311,7 +7347,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>32060</t>
+          <t>32350</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7321,17 +7357,17 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی اصفهان</t>
+          <t>دانشگاه علوم پزشکی تهران</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -7345,7 +7381,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>4</v>
@@ -7354,16 +7390,16 @@
       <c r="L103" s="2" t="inlineStr"/>
       <c r="M103" s="2" t="inlineStr"/>
       <c r="N103" s="2" t="inlineStr"/>
-      <c r="O103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P103" s="2" t="inlineStr"/>
-      <c r="Q103" s="2" t="inlineStr">
-        <is>
-          <t>محدودیت در ارائه خوابگاه</t>
-        </is>
-      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7409,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>32291</t>
+          <t>32391</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -7383,7 +7419,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی ایران</t>
+          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -7407,7 +7443,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>4</v>
@@ -7422,14 +7458,10 @@
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr"/>
-      <c r="Q104" s="2" t="inlineStr">
-        <is>
-          <t>دارای خوابگاه ملکی</t>
-        </is>
-      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7471,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>32350</t>
+          <t>32427</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -7449,7 +7481,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تهران</t>
+          <t>دانشگاه علوم توانبخشی و سلامت اجتماعی - تهران</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -7473,7 +7505,7 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>4</v>
@@ -7491,7 +7523,7 @@
       <c r="Q105" s="2" t="inlineStr"/>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7533,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>32391</t>
+          <t>32658</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -7511,12 +7543,12 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
+          <t>دانشگاه علوم پزشکی مشهد</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>خراسان رضوی</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -7535,7 +7567,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>4</v>
@@ -7550,10 +7582,14 @@
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr"/>
-      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
+        </is>
+      </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7599,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>32427</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -7573,12 +7609,12 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم توانبخشی و سلامت اجتماعی - تهران</t>
+          <t>دانشگاه علوم پزشکی تبریز</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>آذربایجان شرقی</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -7593,11 +7629,11 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>4</v>
@@ -7615,7 +7651,7 @@
       <c r="Q107" s="2" t="inlineStr"/>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7661,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>32658</t>
+          <t>34093</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -7635,12 +7671,12 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی مشهد</t>
+          <t>دانشگاه علوم پزشکی یزد</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>خراسان رضوی</t>
+          <t>یزد</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -7655,11 +7691,11 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>4</v>
@@ -7681,7 +7717,7 @@
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>122</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7727,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>32418</t>
+          <t>32464</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7701,17 +7737,17 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
+          <t>دانشگاه علوم پزشکی شهرکرد</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>چهارمحال و بختیاری</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -7725,7 +7761,7 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>4</v>
@@ -7734,16 +7770,20 @@
       <c r="L109" s="2" t="inlineStr"/>
       <c r="M109" s="2" t="inlineStr"/>
       <c r="N109" s="2" t="inlineStr"/>
-      <c r="O109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P109" s="2" t="inlineStr"/>
       <c r="Q109" s="2" t="inlineStr">
         <is>
-          <t>فاقد خوابگاه</t>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>65</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7793,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>32817</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -7763,17 +7803,17 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم توانبخشی و سلامت اجتماعی - تهران</t>
+          <t>دانشگاه علوم پزشکی جندیشاپور - اهواز</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>خوزستان</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -7787,7 +7827,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>4</v>
@@ -7796,12 +7836,16 @@
       <c r="L110" s="2" t="inlineStr"/>
       <c r="M110" s="2" t="inlineStr"/>
       <c r="N110" s="2" t="inlineStr"/>
-      <c r="O110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P110" s="2" t="inlineStr"/>
       <c r="Q110" s="2" t="inlineStr"/>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>77</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7855,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>31829</t>
+          <t>33006</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -7821,12 +7865,12 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تبریز</t>
+          <t>دانشگاه علوم پزشکی سمنان</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>آذربایجان شرقی</t>
+          <t>سمنان</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -7841,11 +7885,11 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>4</v>
@@ -7860,10 +7904,14 @@
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr"/>
-      <c r="Q111" s="2" t="inlineStr"/>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>محدودیت در ارائه خوابگاه</t>
+        </is>
+      </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>83</t>
         </is>
       </c>
     </row>
@@ -7873,7 +7921,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>34093</t>
+          <t>33133</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -7883,12 +7931,12 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی یزد</t>
+          <t>دانشگاه علوم پزشکی زاهدان</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>یزد</t>
+          <t>سیستان و بلوچستان</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -7903,11 +7951,11 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>4</v>
@@ -7929,7 +7977,7 @@
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>87</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7987,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>32678</t>
+          <t>33503</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -7949,17 +7997,17 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی مشهد</t>
+          <t>دانشگاه علوم پزشکی کرمان</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>خراسان رضوی</t>
+          <t>کرمان</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -7973,7 +8021,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>4</v>
@@ -7981,21 +8029,21 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr"/>
       <c r="M113" s="2" t="inlineStr"/>
-      <c r="N113" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P113" s="2" t="inlineStr"/>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -8005,7 +8053,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>31852</t>
+          <t>33565</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8015,17 +8063,17 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تبریز</t>
+          <t>دانشگاه علوم پزشکی کرمانشاه</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>آذربایجان شرقی</t>
+          <t>کرمانشاه</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -8035,11 +8083,11 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>4</v>
@@ -8048,16 +8096,20 @@
       <c r="L114" s="2" t="inlineStr"/>
       <c r="M114" s="2" t="inlineStr"/>
       <c r="N114" s="2" t="inlineStr"/>
-      <c r="O114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P114" s="2" t="inlineStr"/>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>فاقد خوابگاه</t>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>104</t>
         </is>
       </c>
     </row>
@@ -8067,7 +8119,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>32464</t>
+          <t>33671</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8077,12 +8129,12 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شهرکرد</t>
+          <t>دانشگاه علوم پزشکی گیلان - رشت</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>چهارمحال و بختیاری</t>
+          <t>گیلان</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -8101,7 +8153,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>4</v>
@@ -8116,14 +8168,14 @@
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr"/>
-      <c r="Q115" s="2" t="inlineStr">
-        <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+      <c r="Q115" s="3" t="inlineStr">
+        <is>
+          <t>محل تحصیل دانشکده پزشکی - عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>107</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8185,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>32817</t>
+          <t>33781</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8143,12 +8195,12 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی جندیشاپور - اهواز</t>
+          <t>دانشگاه علوم پزشکی بابل</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>خوزستان</t>
+          <t>مازندران</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -8167,7 +8219,7 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>4</v>
@@ -8182,10 +8234,14 @@
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr"/>
-      <c r="Q116" s="2" t="inlineStr"/>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>فاقد خوابگاه</t>
+        </is>
+      </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>112</t>
         </is>
       </c>
     </row>
@@ -8195,7 +8251,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>33006</t>
+          <t>34025</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -8205,12 +8261,12 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی سمنان</t>
+          <t>دانشگاه علوم پزشکی همدان</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>سمنان</t>
+          <t>همدان</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -8229,7 +8285,7 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>4</v>
@@ -8246,12 +8302,12 @@
       <c r="P117" s="2" t="inlineStr"/>
       <c r="Q117" s="2" t="inlineStr">
         <is>
-          <t>محدودیت در ارائه خوابگاه</t>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>120</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8317,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>33133</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -8271,17 +8327,17 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی زاهدان</t>
+          <t>دانشگاه علوم پزشکی شیراز</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>سیستان و بلوچستان</t>
+          <t>فارس</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>روزانه</t>
+          <t>شهریه پرداز</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -8295,7 +8351,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>4</v>
@@ -8304,20 +8360,16 @@
       <c r="L118" s="2" t="inlineStr"/>
       <c r="M118" s="2" t="inlineStr"/>
       <c r="N118" s="2" t="inlineStr"/>
-      <c r="O118" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O118" s="2" t="inlineStr"/>
       <c r="P118" s="2" t="inlineStr"/>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>91</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8379,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>33503</t>
+          <t>32060</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -8337,17 +8389,17 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی کرمان</t>
+          <t>دانشگاه علوم پزشکی اصفهان</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>کرمان</t>
+          <t>اصفهان</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>روزانه</t>
+          <t>شهریه پرداز</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -8361,7 +8413,7 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>4</v>
@@ -8370,20 +8422,16 @@
       <c r="L119" s="2" t="inlineStr"/>
       <c r="M119" s="2" t="inlineStr"/>
       <c r="N119" s="2" t="inlineStr"/>
-      <c r="O119" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr"/>
       <c r="Q119" s="2" t="inlineStr">
         <is>
-          <t>فاقد خوابگاه</t>
+          <t>محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -8393,7 +8441,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>33565</t>
+          <t>32418</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -8403,17 +8451,17 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی کرمانشاه</t>
+          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>کرمانشاه</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>روزانه</t>
+          <t>شهریه پرداز</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -8427,7 +8475,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>4</v>
@@ -8436,20 +8484,16 @@
       <c r="L120" s="2" t="inlineStr"/>
       <c r="M120" s="2" t="inlineStr"/>
       <c r="N120" s="2" t="inlineStr"/>
-      <c r="O120" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O120" s="2" t="inlineStr"/>
       <c r="P120" s="2" t="inlineStr"/>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -8525,7 +8569,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>33236</t>
+          <t>32191</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -8535,17 +8579,17 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شیراز</t>
+          <t>دانشگاه علوم پزشکی بوشهر</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>بوشهر</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -8559,7 +8603,7 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>5</v>
@@ -8568,16 +8612,20 @@
       <c r="L122" s="2" t="inlineStr"/>
       <c r="M122" s="2" t="inlineStr"/>
       <c r="N122" s="2" t="inlineStr"/>
-      <c r="O122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P122" s="2" t="inlineStr"/>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>فاقد خوابگاه</t>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8635,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>32191</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -8597,12 +8645,12 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی بوشهر</t>
+          <t>دانشگاه علوم پزشکی اصفهان</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>بوشهر</t>
+          <t>اصفهان</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -8621,7 +8669,7 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>5</v>
@@ -8638,12 +8686,12 @@
       <c r="P123" s="2" t="inlineStr"/>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+          <t>محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -8653,7 +8701,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>32030</t>
+          <t>33187</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -8663,12 +8711,12 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی اصفهان</t>
+          <t>دانشگاه علوم پزشکی جهرم</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>فارس</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -8687,7 +8735,7 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>5</v>
@@ -8709,7 +8757,7 @@
       </c>
       <c r="R124" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8767,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>32209</t>
+          <t>33268</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -8727,19 +8775,19 @@
           <t>علوم آزمایشگاهی</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>دانشگاه علوم پزشکی بوشهر</t>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>دانشگاه علوم پزشکی شیراز (محل تحصیل دانشکده علوم پزشکی جنوب شرق استان فارس (داراب))</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>بوشهر</t>
+          <t>فارس</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -8753,7 +8801,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>5</v>
@@ -8762,16 +8810,20 @@
       <c r="L125" s="2" t="inlineStr"/>
       <c r="M125" s="2" t="inlineStr"/>
       <c r="N125" s="2" t="inlineStr"/>
-      <c r="O125" s="2" t="inlineStr"/>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P125" s="2" t="inlineStr"/>
-      <c r="Q125" s="2" t="inlineStr">
-        <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+      <c r="Q125" s="3" t="inlineStr">
+        <is>
+          <t>ممنوعیت نقل و انتقال - معرفی به خوابگاههای خودگردان</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>92</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8833,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>33187</t>
+          <t>33294</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -8791,7 +8843,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی جهرم</t>
+          <t>دانشگاه علوم پزشکی فسا</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -8815,7 +8867,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>5</v>
@@ -8832,12 +8884,12 @@
       <c r="P126" s="2" t="inlineStr"/>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>محدودیت در ارائه خوابگاه</t>
+          <t>سال اول معرفی به خوابگاه خودگردان</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>94</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8899,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>33268</t>
+          <t>33305</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -8857,7 +8909,7 @@
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شیراز (محل تحصیل دانشکده علوم پزشکی جنوب شرق استان فارس (داراب))</t>
+          <t>دانشکده علوم پزشکی و خدمات بهداشتی درمانی گراش</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -8881,7 +8933,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>5</v>
@@ -8896,14 +8948,14 @@
         </is>
       </c>
       <c r="P127" s="2" t="inlineStr"/>
-      <c r="Q127" s="3" t="inlineStr">
-        <is>
-          <t>ممنوعیت نقل و انتقال - معرفی به خوابگاههای خودگردان</t>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>دارای خوابگاه ملکی</t>
         </is>
       </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8965,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>33294</t>
+          <t>33962</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -8923,12 +8975,12 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی فسا</t>
+          <t>دانشگاه علوم پزشکی بندرعباس</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>هرمزگان</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -8947,7 +8999,7 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>5</v>
@@ -8964,12 +9016,12 @@
       <c r="P128" s="2" t="inlineStr"/>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>سال اول معرفی به خوابگاه خودگردان</t>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -8979,7 +9031,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>33305</t>
+          <t>33259</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -8989,7 +9041,7 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>دانشکده علوم پزشکی و خدمات بهداشتی درمانی گراش</t>
+          <t>دانشگاه علوم پزشکی شیراز (محل تحصیل دانشکده پیراپزشکی استهبان)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -9009,11 +9061,11 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>5</v>
@@ -9028,14 +9080,14 @@
         </is>
       </c>
       <c r="P129" s="2" t="inlineStr"/>
-      <c r="Q129" s="2" t="inlineStr">
-        <is>
-          <t>دارای خوابگاه ملکی</t>
+      <c r="Q129" s="3" t="inlineStr">
+        <is>
+          <t>ممنوعیت نقل و انتقال - معرفی به خوابگاههای خودگردان</t>
         </is>
       </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>92</t>
         </is>
       </c>
     </row>
@@ -9045,7 +9097,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>32056</t>
+          <t>32287</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -9055,17 +9107,17 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی اصفهان</t>
+          <t>دانشگاه علوم پزشکی ایران</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>اصفهان</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -9079,7 +9131,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>5</v>
@@ -9088,16 +9140,20 @@
       <c r="L130" s="2" t="inlineStr"/>
       <c r="M130" s="2" t="inlineStr"/>
       <c r="N130" s="2" t="inlineStr"/>
-      <c r="O130" s="2" t="inlineStr"/>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P130" s="2" t="inlineStr"/>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>معرفی به خوابگاههای خودگردان</t>
+          <t>دارای خوابگاه ملکی</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9163,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>33962</t>
+          <t>32346</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -9117,12 +9173,12 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی بندرعباس</t>
+          <t>دانشگاه علوم پزشکی تهران</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>هرمزگان</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -9141,7 +9197,7 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>5</v>
@@ -9156,14 +9212,10 @@
         </is>
       </c>
       <c r="P131" s="2" t="inlineStr"/>
-      <c r="Q131" s="2" t="inlineStr">
-        <is>
-          <t>فاقد خوابگاه</t>
-        </is>
-      </c>
+      <c r="Q131" s="2" t="inlineStr"/>
       <c r="R131" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>61</t>
         </is>
       </c>
     </row>
@@ -9173,7 +9225,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>33259</t>
+          <t>32382</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -9181,14 +9233,14 @@
           <t>علوم آزمایشگاهی</t>
         </is>
       </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>دانشگاه علوم پزشکی شیراز (محل تحصیل دانشکده پیراپزشکی استهبان)</t>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>فارس</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -9203,11 +9255,11 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>بهمن</t>
+          <t>مهر</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>5</v>
@@ -9222,14 +9274,10 @@
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr"/>
-      <c r="Q132" s="3" t="inlineStr">
-        <is>
-          <t>ممنوعیت نقل و انتقال - معرفی به خوابگاههای خودگردان</t>
-        </is>
-      </c>
+      <c r="Q132" s="2" t="inlineStr"/>
       <c r="R132" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9287,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>32287</t>
+          <t>33963</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -9249,12 +9297,12 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی ایران</t>
+          <t>دانشگاه علوم پزشکی بندرعباس</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>هرمزگان</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -9269,11 +9317,11 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>مهر</t>
+          <t>بهمن</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>5</v>
@@ -9290,12 +9338,12 @@
       <c r="P133" s="2" t="inlineStr"/>
       <c r="Q133" s="2" t="inlineStr">
         <is>
-          <t>دارای خوابگاه ملکی</t>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R133" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -9305,7 +9353,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>32346</t>
+          <t>32083</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -9315,12 +9363,12 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی تهران</t>
+          <t>دانشگاه علوم پزشکی کاشان</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>اصفهان</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -9339,7 +9387,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J134" s="2" t="n">
         <v>5</v>
@@ -9354,10 +9402,14 @@
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr"/>
-      <c r="Q134" s="2" t="inlineStr"/>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
+        </is>
+      </c>
       <c r="R134" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9419,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>32382</t>
+          <t>33610</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -9377,12 +9429,12 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
+          <t>دانشگاه علوم پزشکی یاسوج</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>کهگیلویه و بویراحمد</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -9416,10 +9468,14 @@
         </is>
       </c>
       <c r="P135" s="2" t="inlineStr"/>
-      <c r="Q135" s="2" t="inlineStr"/>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>فاقد خوابگاه</t>
+        </is>
+      </c>
       <c r="R135" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>105</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9485,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>33963</t>
+          <t>32383</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -9439,12 +9495,12 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی بندرعباس</t>
+          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>هرمزگان</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -9463,7 +9519,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>5</v>
@@ -9478,14 +9534,10 @@
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr"/>
-      <c r="Q136" s="2" t="inlineStr">
-        <is>
-          <t>فاقد خوابگاه</t>
-        </is>
-      </c>
+      <c r="Q136" s="2" t="inlineStr"/>
       <c r="R136" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9803,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>32302</t>
+          <t>33111</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -9761,17 +9813,17 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی ایران</t>
+          <t>دانشگاه علوم پزشکی زاهدان</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>سیستان و بلوچستان</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -9785,7 +9837,7 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>6</v>
@@ -9793,21 +9845,21 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr"/>
       <c r="M141" s="2" t="inlineStr"/>
-      <c r="N141" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr"/>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P141" s="2" t="inlineStr"/>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>فاقد خوابگاه</t>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
         </is>
       </c>
       <c r="R141" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>87</t>
         </is>
       </c>
     </row>
@@ -9817,7 +9869,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>32403</t>
+          <t>33801</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -9827,17 +9879,17 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
+          <t>دانشگاه علوم پزشکی مازندران - ساری</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>مازندران</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -9851,7 +9903,7 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>6</v>
@@ -9860,16 +9912,16 @@
       <c r="L142" s="2" t="inlineStr"/>
       <c r="M142" s="2" t="inlineStr"/>
       <c r="N142" s="2" t="inlineStr"/>
-      <c r="O142" s="2" t="inlineStr"/>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P142" s="2" t="inlineStr"/>
-      <c r="Q142" s="2" t="inlineStr">
-        <is>
-          <t>فاقد خوابگاه</t>
-        </is>
-      </c>
+      <c r="Q142" s="2" t="inlineStr"/>
       <c r="R142" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>112</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9931,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>32670</t>
+          <t>32302</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -9889,12 +9941,12 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی مشهد</t>
+          <t>دانشگاه علوم پزشکی ایران</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>خراسان رضوی</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -9913,7 +9965,7 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J143" s="2" t="n">
         <v>6</v>
@@ -9921,17 +9973,21 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr"/>
       <c r="M143" s="2" t="inlineStr"/>
-      <c r="N143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O143" s="2" t="inlineStr"/>
       <c r="P143" s="2" t="inlineStr"/>
       <c r="Q143" s="2" t="inlineStr">
         <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R143" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -9941,7 +9997,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>32403</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -9951,17 +10007,17 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی زاهدان</t>
+          <t>دانشگاه علوم پزشکی شهید بهشتی - تهران</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>سیستان و بلوچستان</t>
+          <t>تهران</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>روزانه</t>
+          <t>شهریه پرداز</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -9975,7 +10031,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J144" s="2" t="n">
         <v>6</v>
@@ -9984,20 +10040,16 @@
       <c r="L144" s="2" t="inlineStr"/>
       <c r="M144" s="2" t="inlineStr"/>
       <c r="N144" s="2" t="inlineStr"/>
-      <c r="O144" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O144" s="2" t="inlineStr"/>
       <c r="P144" s="2" t="inlineStr"/>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+          <t>فاقد خوابگاه</t>
         </is>
       </c>
       <c r="R144" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10059,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>33801</t>
+          <t>32670</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -10017,17 +10069,17 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی مازندران - ساری</t>
+          <t>دانشگاه علوم پزشکی مشهد</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>مازندران</t>
+          <t>خراسان رضوی</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>روزانه</t>
+          <t>شهریه پرداز</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -10041,7 +10093,7 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J145" s="2" t="n">
         <v>6</v>
@@ -10050,16 +10102,16 @@
       <c r="L145" s="2" t="inlineStr"/>
       <c r="M145" s="2" t="inlineStr"/>
       <c r="N145" s="2" t="inlineStr"/>
-      <c r="O145" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr"/>
-      <c r="Q145" s="2" t="inlineStr"/>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>عدم تعهد در واگذاری خوابگاه</t>
+        </is>
+      </c>
       <c r="R145" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -10333,7 +10385,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>32210</t>
+          <t>33275</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -10341,19 +10393,19 @@
           <t>علوم تغذیه</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>دانشگاه علوم پزشکی بوشهر</t>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>دانشگاه علوم پزشکی شیراز (محل تحصیل مجتمع آموزش عالی سلامت سپیدان)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>بوشهر</t>
+          <t>فارس</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>شهریه پرداز</t>
+          <t>روزانه</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -10367,7 +10419,7 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J150" s="2" t="n">
         <v>7</v>
@@ -10376,16 +10428,20 @@
       <c r="L150" s="2" t="inlineStr"/>
       <c r="M150" s="2" t="inlineStr"/>
       <c r="N150" s="2" t="inlineStr"/>
-      <c r="O150" s="2" t="inlineStr"/>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P150" s="2" t="inlineStr"/>
-      <c r="Q150" s="2" t="inlineStr">
-        <is>
-          <t>عدم تعهد در واگذاری خوابگاه</t>
+      <c r="Q150" s="3" t="inlineStr">
+        <is>
+          <t>ممنوعیت نقل و انتقال - محدودیت در ارائه خوابگاه</t>
         </is>
       </c>
       <c r="R150" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>93</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10451,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>33275</t>
+          <t>33323</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -10405,7 +10461,7 @@
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>دانشگاه علوم پزشکی شیراز (محل تحصیل مجتمع آموزش عالی سلامت سپیدان)</t>
+          <t>دانشکده علوم پزشکی و خدمات بهداشتی درمانی لارستان (محل تحصیل دانشکده بهداشت شهرستان اوز)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -10429,7 +10485,7 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J151" s="2" t="n">
         <v>7</v>
@@ -10446,12 +10502,12 @@
       <c r="P151" s="2" t="inlineStr"/>
       <c r="Q151" s="3" t="inlineStr">
         <is>
-          <t>ممنوعیت نقل و انتقال - محدودیت در ارائه خوابگاه</t>
+          <t>انجام کلیه کارآموزی ها و کارآموزی درعرصه ها در شهرستانهای لار و اوز می باشد.</t>
         </is>
       </c>
       <c r="R151" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
     </row>
@@ -10467,7 +10523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10576,7 +10632,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D6" s="2">
         <f>COUNTIF('لیست'!$J$2:$J$151,A6)</f>
@@ -10610,7 +10666,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D8" s="2">
         <f>COUNTIF('لیست'!$J$2:$J$151,A8)</f>
@@ -10651,195 +10707,173 @@
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>آزاد تمام وقت</t>
-        </is>
-      </c>
-      <c r="B13" s="2">
-        <f>COUNTIF('لیست'!$F$2:$F$151,A13)</f>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>پرچم</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>تعداد</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>تعهد خدمت</t>
+        </is>
+      </c>
+      <c r="B15" s="2">
+        <f>COUNTIF('لیست'!$K$2:$K$151,"✓")</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>خودگردان آزاد</t>
-        </is>
-      </c>
-      <c r="B14" s="2">
-        <f>COUNTIF('لیست'!$F$2:$F$151,A14)</f>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>مصاحبه/شرایط خاص</t>
+        </is>
+      </c>
+      <c r="B16" s="2">
+        <f>COUNTIF('لیست'!$L$2:$L$151,"✓")</f>
         <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>پرچم</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>تعداد</t>
-        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>تعهد خدمت</t>
+          <t>فقط بومی</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIF('لیست'!$K$2:$K$151,"✓")</f>
+        <f>COUNTIF('لیست'!$M$2:$M$151,"✓")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>مصاحبه/شرایط خاص</t>
+          <t>ظرفیت کم</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIF('لیست'!$L$2:$L$151,"✓")</f>
+        <f>COUNTIF('لیست'!$N$2:$N$151,"✓")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>فقط بومی</t>
+          <t>محرومیت کنکور بعد</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIF('لیست'!$M$2:$M$151,"✓")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>ظرفیت کم</t>
-        </is>
-      </c>
-      <c r="B20" s="2">
-        <f>COUNTIF('لیست'!$N$2:$N$151,"✓")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>محرومیت کنکور بعد</t>
-        </is>
-      </c>
-      <c r="B21" s="2">
         <f>COUNTIF('لیست'!$O$2:$O$151,"✓")</f>
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>مراحل فیلتر (خروجی build_list.py)</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>ردیف باقی‌مانده</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>کل ردیف‌های دفترچه</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>13397</v>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>مراحل فیلتر (خروجی build_list.py)</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>ردیف باقی‌مانده</t>
-        </is>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>فقط «با آزمون» (کدهای فرم ۱۵۰تایی)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>4345</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>کل ردیف‌های دفترچه</t>
+          <t>حذف کدهای تکراری بین گروه‌ها</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>13397</v>
+        <v>4345</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>فقط «با آزمون» (کدهای فرم ۱۵۰تایی)</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>در رشته‌های مورد علاقهٔ داوطلب (و دوره‌های مجاز)</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>4345</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>حذف کدهای تکراری بین گروه‌ها</t>
+          <t>جنسیت سازگار</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>4345</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>در رشته‌های مورد علاقهٔ داوطلب (و دوره‌های مجاز)</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>حذف «ویژه بهیاران»</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>1257</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>جنسیت سازگار</t>
+          <t>حذف مصاحبه، بورس و گزینش</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1183</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>حذف «ویژه بهیاران»</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>حذف کدهای «مخصوص بومی» که داوطلب شرایطش را ندارد</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1183</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>حذف مصاحبه، بورس و گزینش</t>
+          <t>تعهد خدمت فقط با رضایت (و در استان‌های مجاز)</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>حذف کدهای «مخصوص بومی» که داوطلب شرایطش را ندارد</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>تعهد خدمت فقط با رضایت (و در استان‌های مجاز)</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>601</v>
+        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -10853,7 +10887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10935,55 +10969,55 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>field</t>
+          <t>course_order</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>[["روزانه", "روزانه - غیردولتی"], "شهریه پرداز", ["آزاد تمام وقت", "خودگردان آزاد"], "پردیس خودگردان", "نوبت دوم"]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>preferred_provinces</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>["فارس", "بوشهر", "کهگیلویه و بویراحمد", "هرمزگان", "اصفهان", "یزد", "تهران"]</t>
+          <t>course_priority</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>within_field</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>preferred_universities</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>field</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>excluded_provinces</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>preferred_provinces</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>["فارس", "بوشهر", "کهگیلویه و بویراحمد", "هرمزگان", "اصفهان", "یزد", "تهران"]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>excluded_universities</t>
+          <t>preferred_universities</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -10995,79 +11029,79 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>accept_commitment</t>
+          <t>excluded_provinces</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>["فارس"]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>accept_interview</t>
+          <t>excluded_universities</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>accept_start_1406</t>
+          <t>accept_commitment</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>["فارس"]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>accept_start_bahman</t>
+          <t>accept_interview</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>is_behyar</t>
+          <t>accept_start_1406</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>special_native_quota</t>
+          <t>accept_start_bahman</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>retake_next_year</t>
+          <t>is_behyar</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -11079,34 +11113,58 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>max_codes</t>
+          <t>special_native_quota</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>choices</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>[{"title": "دکتری عمومی پزشکی"}, {"title": "دکتری عمومی دندانپزشکی"}, {"title": "دکتری عمومی داروسازی"}, {"title": "فیزیوتراپی"}, {"title": "علوم آزمایشگاهی"}, {"title": "بینایی سنجی"}, {"title": "علوم تغذیه"}]</t>
+          <t>retake_next_year</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>max_codes</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>choices</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>[{"title": "دکتری عمومی پزشکی"}, {"title": "دکتری عمومی دندانپزشکی"}, {"title": "دکتری عمومی داروسازی"}, {"title": "فیزیوتراپی"}, {"title": "علوم آزمایشگاهی"}, {"title": "بینایی سنجی"}, {"title": "علوم تغذیه"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>از فرم تلگرام: پرستاری و مامایی نمی‌خواهد؛ انتخاب رشتهٔ آزاد (غیرپزشکی) را هم می‌خواهد.</t>
         </is>
@@ -11139,21 +11197,21 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>451 کد مناسب دیگر به خاطر سقف 150 کنار رفت (از هر رشته، کدهای با ترجیح کمتر).</t>
+          <t>447 کد مناسب دیگر به خاطر سقف 150 کنار رفت (از هر رشته، کدهای با ترجیح کمتر).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>136 کد محرومیت از کنکور سال بعد دارند (روزانه، یا پزشکی/دندان/دارو/دامپزشکی در هر دوره).</t>
+          <t>143 کد محرومیت از کنکور سال بعد دارند (روزانه، یا پزشکی/دندان/دارو/دامپزشکی در هر دوره).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>15 کد تعهد خدمت دارند.</t>
+          <t>20 کد تعهد خدمت دارند.</t>
         </is>
       </c>
     </row>
@@ -11167,14 +11225,14 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>11 کد ظرفیت ۱ یا ۲ نفر دارند.</t>
+          <t>4 کد ظرفیت ۱ یا ۲ نفر دارند.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>30 کد شروع غیر از مهر دارند (بهمن یا مهر ۱۴۰۶).</t>
+          <t>24 کد شروع غیر از مهر دارند (بهمن یا مهر ۱۴۰۶).</t>
         </is>
       </c>
     </row>
